--- a/submission/knowledge/A12-武汉游记助手/武汉游记助手QA导入表.xlsx
+++ b/submission/knowledge/A12-武汉游记助手/武汉游记助手QA导入表.xlsx
@@ -367,6 +367,584 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">没进武大能写樱花大道吗？</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能写进校。可写预约失败或改去的东湖江滩。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">樱花</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">没进黄鹤楼？</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写门外或江滩，不编楼内。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">满载</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雨天改省博？</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">预约进去了才能写馆内。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雨</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写征服蛇山？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不写。量力即可。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">老人</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写走失？</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">除非用户要记录且已安全结束，否则不要渲染。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小孩</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江滩看灯怎么写？</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写免费看江和真实天气。不要写成进场演出票。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">灯光</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">游船取消了？</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写取消和改去的地方，不编开航。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">没去古琴台能写知音吗？</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要硬写。去了再写典故，并标明传说。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知音</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">抄崔颢可以吗？</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公开名句可以。同时写今楼是重建。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">诗</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必须写江城知音吗？</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不强制。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广告</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能写全网第一吗？</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。不写未核对的排行和永久票价。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原则</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能编没去的编钟近景吗？</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。没进省博就不要写柜前细节。</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原则</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能写黄牛带我们进去吗？</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要写成攻略。可以写「走官方预约」。</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原则</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只在园外怎么写？</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写蛇山轮廓、江风、没入园。不写楼内展陈。</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日场和夜场都去了？</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分开写两套票、两种体验。不要混成一张票。</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只走了听涛能写磨山全景吗？</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。听涛写沿岸；磨山、樱园要真的进了才写。</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">没坐游船能写湖心吗？</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要写成已经上船。可写岸上所见。</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">没吃热干面能写正宗一碗吗？</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按实际吃的写。可写过早习俗，不点未进的店。</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">过早</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">户部巷和吉庆街写混可以吗？</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要。一个在武昌，一个在汉口。</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">过早</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只在汉口能写两江三镇走穿吗？</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。按真实过江次数写。</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三镇</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">免费看灯写成买了秀票？</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要。江滩看照明通常免费；夜上黄鹤楼、游船另写。</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜景</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">游船取消怎么收尾？</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写取消和改去的江滩或酒店，不编开航。</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜景</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武大门外能写校园花海吗？</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能写进校。可写预约失败或改去的东湖、江滩。</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">樱花</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小孩哭闹怎么写？</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可写真实疲惫，不嘲讽、不渲染走失惊悚。</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">家庭</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">老人没登顶算失败吗？</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不写失败。量力、江风、休息即可。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">家庭</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">去了古琴台怎么点一句？</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伯牙子期是传说。标明典故，不写成考古直播。</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知音</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋雨没进馆？</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写雨和改线。不要写编钟就在眼前。</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雨</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两行不够地名怎么办？</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地名+一件真事。不要堆四个没去的点。</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海报</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">给外国人写一段？</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可以短写，专名用约定译法，数字仍不编。</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英文</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用网图冒充现场？</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要。用户自摄。</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">配图</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必须@江城知音吗？</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不强制。不写参赛术语。</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广告</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">帮我写酒店差评泄愤？</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不写人身攻击。住宿细节问管家，不编房价。</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">把西岭雪山写进来？</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本空间只写武汉实际走过的点。</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼进不去的朋友圈？</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写门外或江滩。不编楼内。</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">满载</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>